--- a/jira_export_2026-10-29.xlsx
+++ b/jira_export_2026-10-29.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>71,994 €</t>
+          <t>72,853 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,14 +760,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>23,984 €</t>
+          <t>24,320 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>47,800 €</t>
+          <t>48,323 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -5173,10 +5173,10 @@
         <v>0</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>258</v>
+        <v>301</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>86</v>
+        <v>100.33</v>
       </c>
     </row>
     <row r="63">
@@ -5317,10 +5317,10 @@
         <v>0</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>203.5</v>
+        <v>407</v>
       </c>
       <c r="P64" s="15" t="n">
-        <v>203.5</v>
+        <v>407</v>
       </c>
     </row>
     <row r="65">
@@ -5525,7 +5525,7 @@
         <v>2500</v>
       </c>
       <c r="O67" s="16" t="n">
-        <v>0</v>
+        <v>319.08</v>
       </c>
       <c r="P67" s="12" t="n">
         <v>0</v>
@@ -9963,10 +9963,10 @@
         <v>3016.08</v>
       </c>
       <c r="O129" s="16" t="n">
-        <v>2178.28</v>
+        <v>2471.51</v>
       </c>
       <c r="P129" s="12" t="n">
-        <v>181.52</v>
+        <v>205.96</v>
       </c>
     </row>
     <row r="130">
@@ -12911,10 +12911,10 @@
         <v>65426.36599999999</v>
       </c>
       <c r="O177" s="18" t="n">
-        <v>71994.39199999999</v>
+        <v>72853.202</v>
       </c>
       <c r="P177" s="18" t="n">
-        <v>224.07</v>
+        <v>226.74</v>
       </c>
     </row>
   </sheetData>
@@ -14905,16 +14905,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>477227</v>
+        <v>476368</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>200550</v>
+        <v>200303</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>276677</v>
+        <v>276065</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>217956</v>
+        <v>217343</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>16308</v>
@@ -14930,16 +14930,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>247537</v>
+        <v>247201</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>65008</v>
+        <v>64965</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>182529</v>
+        <v>182236</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>163318</v>
+        <v>163024</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>
@@ -14955,16 +14955,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>226590</v>
+        <v>226067</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>132442</v>
+        <v>132238</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>94148</v>
+        <v>93829</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>54638</v>
+        <v>54319</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>7133</v>

--- a/jira_export_2026-10-29.xlsx
+++ b/jira_export_2026-10-29.xlsx
@@ -226,7 +226,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -286,6 +286,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -720,7 +723,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>72,853 €</t>
+          <t>73,453 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +737,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +763,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>24,320 €</t>
+          <t>24,920 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -891,16 +894,16 @@
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>303</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -916,7 +919,7 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B29" s="7" t="n"/>
@@ -8202,7 +8205,7 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Modélisation 5j</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -10033,10 +10036,10 @@
         <v>0</v>
       </c>
       <c r="O130" s="15" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="P130" s="15" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="131">
@@ -12911,10 +12914,10 @@
         <v>65426.36599999999</v>
       </c>
       <c r="O177" s="18" t="n">
-        <v>72853.202</v>
+        <v>73453.202</v>
       </c>
       <c r="P177" s="18" t="n">
-        <v>226.74</v>
+        <v>228.61</v>
       </c>
     </row>
   </sheetData>
@@ -14905,16 +14908,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>476368</v>
+        <v>475768</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>200303</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>276065</v>
+        <v>275465</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>217343</v>
+        <v>216743</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>16308</v>
@@ -14930,16 +14933,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>247201</v>
+        <v>246601</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>64965</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>182236</v>
+        <v>181636</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>163024</v>
+        <v>162424</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>
@@ -16341,7 +16344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -16362,7 +16365,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>13 clôture(s) : 13 projet(s), 0 rework</t>
+          <t>14 clôture(s) : 13 projet(s), 1 rework</t>
         </is>
       </c>
     </row>
@@ -16789,33 +16792,63 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>PDMDEP-18240</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en servi</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Biarritz</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n">
-        <v>0</v>
+      <c r="B21" s="28" t="n"/>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="28" t="n"/>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="28" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-10-29.xlsx
+++ b/jira_export_2026-10-29.xlsx
@@ -723,7 +723,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>74,574 €</t>
+          <t>74,760 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -737,7 +737,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -763,7 +763,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>25,720 €</t>
+          <t>25,906 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -818,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>515 h</t>
+          <t>547 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -832,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -903,7 +903,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>303</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1768,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>1352</v>
+        <v>1456</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>0</v>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>595.08</v>
+        <v>677.16</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
@@ -12986,10 +12986,10 @@
         <v>65426.366</v>
       </c>
       <c r="O178" s="18" t="n">
-        <v>74573.97199999999</v>
+        <v>74760.052</v>
       </c>
       <c r="P178" s="18" t="n">
-        <v>231.37</v>
+        <v>231.95</v>
       </c>
     </row>
   </sheetData>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>148.08</v>
+        <v>180.08</v>
       </c>
     </row>
   </sheetData>
@@ -14981,16 +14981,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>475382</v>
+        <v>475196</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>199917</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>275465</v>
+        <v>275279</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>216743</v>
+        <v>216557</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>16308</v>
@@ -15006,16 +15006,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>245801</v>
+        <v>245615</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>64165</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>181636</v>
+        <v>181450</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>162424</v>
+        <v>162238</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>
